--- a/unit10_pinMux/unit10_pinMux.xlsx
+++ b/unit10_pinMux/unit10_pinMux.xlsx
@@ -1,10 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28827"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1619F422-14AC-4045-BF2B-18CEC8D16EA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,12 +37,12 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -102,7 +103,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1"/>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -126,20 +133,26 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>198782</xdr:colOff>
       <xdr:row>3</xdr:row>
       <xdr:rowOff>38099</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>22</xdr:col>
-      <xdr:colOff>194937</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>180975</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Picture 2"/>
+      <xdr:colOff>155180</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>1077</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000003000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -152,8 +165,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="209550" y="609599"/>
-          <a:ext cx="4595487" cy="2238376"/>
+          <a:off x="198782" y="554934"/>
+          <a:ext cx="5204259" cy="2030317"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -177,7 +190,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="Picture 3"/>
+        <xdr:cNvPr id="4" name="Picture 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000004000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -215,7 +234,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="6" name="Picture 5"/>
+        <xdr:cNvPr id="6" name="Picture 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000006000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -253,7 +278,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="7" name="Picture 6"/>
+        <xdr:cNvPr id="7" name="Picture 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000007000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -291,7 +322,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="8" name="Picture 7"/>
+        <xdr:cNvPr id="8" name="Picture 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000008000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -329,7 +366,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="9" name="Picture 8"/>
+        <xdr:cNvPr id="9" name="Picture 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000009000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -367,7 +410,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="10" name="Picture 9"/>
+        <xdr:cNvPr id="10" name="Picture 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000A000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -405,7 +454,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="11" name="Picture 10"/>
+        <xdr:cNvPr id="11" name="Picture 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000B000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -693,9 +748,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A2:D70"/>
-  <sheetFormatPr defaultColWidth="3.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="3.09765625" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="2" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
